--- a/data/predictions.xlsx
+++ b/data/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -423,12 +423,14 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,32 +471,181 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>阈值上限</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>参考日期</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>概率</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>结算值</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>结算来源</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Brier</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BTC 10/4 日收盘在 $80,000–$88,000 之间</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>between</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>88000</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9/28–10/2 美国现货 BTC ETF 5 天合计净流入 &gt; 0（Farside）</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BTC 10 月收涨（10/31 收盘 &gt; 9/30 收盘）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>待结算</t>
         </is>
       </c>
     </row>
